--- a/manufacturing_forms/025_fashion_brand_ethical_sourcing_audit_form--manufacturing_forms.xlsx
+++ b/manufacturing_forms/025_fashion_brand_ethical_sourcing_audit_form--manufacturing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -1090,346 +1090,6 @@
         </is>
       </c>
       <c r="C21" t="inlineStr">
-        <is>
-          <t>SA8000</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>certification_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>wrap</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>WRAP</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>certification_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>bsci</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>BSCI</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>certification_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>gots</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>GOTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>certification_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>bsci</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>BSCI</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>certification_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>wrap</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>WRAP</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>certification_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>amfori</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Amfori</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>certification_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>sa8000</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>SA8000</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>certification_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>wrap</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>WRAP</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>certification_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>sedex</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Sedex</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>certification_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>fairtrade</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Fairtrade</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>certification_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>wrap</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>WRAP</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>certification_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>bsci</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>BSCI</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>certification_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>gots</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>GOTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>certification_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>fairtrade</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Fairtrade</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>certification_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>amfori</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Amfori</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>certification_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>bsci</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>BSCI</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>certification_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>wrap</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>WRAP</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>certification_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>sedex</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Sedex</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>certification_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>fairtrade</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Fairtrade</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>certification_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>sa8000</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
         <is>
           <t>SA8000</t>
         </is>
